--- a/spider_jd/标题.xlsx
+++ b/spider_jd/标题.xlsx
@@ -52490,6 +52490,16 @@
           <t>资生堂 悦薇智感紧塑焕白眼霜15ml（焕白眼霜）</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10210868055271.html</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -52497,6 +52507,16 @@
           <t>资生堂 新红妍肌活精华露50ml（第三代）（红腰子精华）</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10034291414689.html</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -52504,6 +52524,16 @@
           <t>资生堂 新红妍肌活精华露75ml（第三代）（红腰子精华）</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10220507955056.html</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -52511,6 +52541,16 @@
           <t>黛珂 保湿美容液60ml（紫苏精华）</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10034252422841.html</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -52518,6 +52558,16 @@
           <t>黛珂 肌源修护精华液50ml（第二代小紫瓶精华）</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>728.2</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100036051363.html</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -52525,6 +52575,16 @@
           <t>黛珂 紫苏精华水150ml（老版）</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10156355197377.html</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -52532,6 +52592,16 @@
           <t>黛珂 紫苏植萃精华水150ml（新版）</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10205835599197.html</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -52539,6 +52609,16 @@
           <t>黛珂 牛油果乳液150ml</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100078176270.html</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -52546,6 +52626,16 @@
           <t>黛珂 紫苏精华水300ml</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>298.4</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10213691808778.html</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -52553,6 +52643,16 @@
           <t>黛珂 牛油果乳液300ml</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100019246180.html</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -52560,6 +52660,16 @@
           <t>黛珂 植物欣韵洗颜泡沫200ml</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100006777344.html</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -52567,6 +52677,16 @@
           <t>黛珂 植物欣韵沁莹化妆水 200ml</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100027717187.html</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -52574,6 +52694,16 @@
           <t>黛珂 植物欣韵弹润乳液 200ml</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033455751.html</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -54366,6 +54496,16 @@
           <t>馥蕾诗经典护唇膏4.3g澄糖当红不让色</t>
         </is>
       </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100034923787.html</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -54373,6 +54513,16 @@
           <t>馥蕾诗经典滋润护唇膏4.3g澄糖玫瑰粉红色</t>
         </is>
       </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100020724735.html</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -54380,6 +54530,16 @@
           <t>馥蕾诗莲花青春保湿霜50ml</t>
         </is>
       </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100036218418.html</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -54387,6 +54547,16 @@
           <t>馥蕾诗莲花青春面膜100ml</t>
         </is>
       </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100020724669.html</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -54394,6 +54564,16 @@
           <t>馥蕾诗玫瑰密集保湿平衡乳100ml</t>
         </is>
       </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100052100050.html</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -54401,6 +54581,16 @@
           <t>馥蕾诗玫瑰密集保湿睡眠面膜70ml</t>
         </is>
       </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100241886095.html</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -54408,6 +54598,16 @@
           <t>馥蕾诗玫瑰面膜100ml</t>
         </is>
       </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100051263414.html</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -54415,6 +54615,16 @@
           <t>馥蕾诗玫瑰润泽密集保湿双萃精华100ml</t>
         </is>
       </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10218387811418.html</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -54422,11 +54632,31 @@
           <t>馥蕾诗莲花青春焕采眼霜15ml</t>
         </is>
       </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100305532694.html</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
           <t>馥蕾诗清新护唇膏4.3g(澄糖元气薄荷色)</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>224.2</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100034923787.html</t>
         </is>
       </c>
     </row>

--- a/spider_jd/标题.xlsx
+++ b/spider_jd/标题.xlsx
@@ -52711,6 +52711,16 @@
           <t>黛珂 多重防晒乳60g</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100107116564.html</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -52718,6 +52728,16 @@
           <t>黛珂 心悦容光丝柔蜜粉00 20g</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100109854511.html</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -52725,6 +52745,16 @@
           <t>黛珂 心悦容光丝柔蜜粉10 20g（哑光）</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100109854511.html</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -52732,6 +52762,16 @@
           <t>黛珂 心悦容光丝柔蜜粉11 20g（珠光）</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10138527528860.html</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -52739,6 +52779,16 @@
           <t>娇韵诗 双萃焕活修护精华露30ml（双萃精华）</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100156790209.html</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -52746,6 +52796,16 @@
           <t>娇韵诗 双萃焕活修护精华露50ml（双萃精华）</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100186454536.html</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -52753,6 +52813,16 @@
           <t>娇韵诗 双萃焕活眼部精华20ml（双萃眼霜）</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100012573523.html</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -52760,6 +52830,16 @@
           <t>娇韵诗 焕颜弹力日霜（滋润型）50ml（弹簧日霜）</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100006271038.html</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -52767,6 +52847,16 @@
           <t>娇韵诗 焕颜弹力日霜 50ml（弹簧日霜）</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100156790215.html</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -52774,11 +52864,31 @@
           <t>娇韵诗 焕颜弹力晚霜（滋润型）50ml（弹簧晚霜）</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100006271038.html</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
           <t>娇韵诗 抚纹身体霜175ml</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100104556664.html</t>
         </is>
       </c>
     </row>

--- a/spider_jd/标题.xlsx
+++ b/spider_jd/标题.xlsx
@@ -52898,6 +52898,16 @@
           <t>娇韵诗 舒柔保湿泡沫洁面乳125ml（棉花籽洁面）</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>239.3</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/255673.html</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -52905,6 +52915,16 @@
           <t>娇韵诗 舒润泡沫洁面乳 125ml</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>239.3</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/255673.html</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -52912,6 +52932,16 @@
           <t>娇韵诗 天然调和身体护理油100ml</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/255613.html</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -52919,6 +52949,16 @@
           <t>娇韵诗 温和化妆水200ml（黄水）</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100060090810.html</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -52926,6 +52966,16 @@
           <t>娇韵诗 青春赋活焕采精华水 200ml（新款粉水/少女水）</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10111212833947.html</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -52933,6 +52983,16 @@
           <t>娇韵诗 焕颜弹力精华水200ml（新款弹簧水）</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100009346360.html</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -52940,6 +53000,16 @@
           <t>香奈儿 柔和净肤泡沫洁面乳150ml（山茶花洁面）</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10203329631083.html</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -52947,6 +53017,16 @@
           <t>菲洛嘉 柔滑亮泽面膜 50ml（十全大补面膜）</t>
         </is>
       </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/2219541.html</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -52954,6 +53034,16 @@
           <t>悦木之源 韦博士灵芝焕能好底子精华水200ml（菌菇水）</t>
         </is>
       </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>329.6</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100018279933.html</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -52961,6 +53051,16 @@
           <t>倩碧 卓越润肤乳125ml（无油）</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>278.2</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100022610040.html</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -52968,6 +53068,16 @@
           <t>倩碧 卓越润肤乳125ml（有油）</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100022610036.html</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -52975,6 +53085,16 @@
           <t>倩碧 匀净淡斑多效精华露30ml（镭射淡斑精华）</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100147759583.html</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -52982,6 +53102,16 @@
           <t>倩碧 匀净淡斑多效精华露50ml（镭射淡斑精华）</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100147759565.html</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -52989,6 +53119,16 @@
           <t>妆前柔润底霜50ml（橘子面霜）</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100035199664.html</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -52996,6 +53136,16 @@
           <t xml:space="preserve">香奈儿 护手霜(清爽/轻盈)50ml (白蛋) </t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10202334500836.html</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -53003,6 +53153,16 @@
           <t xml:space="preserve">香奈儿 护手霜(滋润/丰盈)50ml (白蛋) </t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10202334500836.html</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -53010,6 +53170,16 @@
           <t>香奈儿 智慧紧致护手霜50ml(黑蛋)</t>
         </is>
       </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10202335061778.html</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -53017,6 +53187,16 @@
           <t>祖玛珑护手霜 维他命E护手霜100ml</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100018812715.html</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -53024,6 +53204,16 @@
           <t>祖玛珑润唇膏 维他命E唇蜜15ml</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033356660.html</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -53031,6 +53221,16 @@
           <t xml:space="preserve">祖玛珑护手霜 蓝风铃30ml </t>
         </is>
       </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100311235288.html</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -53038,6 +53238,16 @@
           <t>雅诗兰黛 花漾倾慕唇膏13（420）</t>
         </is>
       </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100230536674.html</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -53045,6 +53255,16 @@
           <t>雅诗兰黛 倾慕唇膏-丝绒系列21（333）</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100042687200.html</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -53052,6 +53272,16 @@
           <t>汤姆福特 烈焰幻魅唇膏15 3g（TF黑管15）</t>
         </is>
       </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>39.51</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10123886664392.html</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -53059,6 +53289,16 @@
           <t>汤姆福特 激情幻魅唇膏16 3g（TF黑管16哑光）</t>
         </is>
       </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10215257990100.html</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -53066,6 +53306,16 @@
           <t>汤姆福特 烈焰幻魅唇膏16 3g（TF黑管16滋润）</t>
         </is>
       </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10145563495545.html</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -53073,6 +53323,16 @@
           <t>阿玛尼 臻致丝绒哑光唇釉 #206 6.5ml（红管206）</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10210920824780.html</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -53080,6 +53340,16 @@
           <t>阿玛尼 臻致丝绒哑光唇釉 #214 6.5ml（红管214）</t>
         </is>
       </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10183990070825.html</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -53087,6 +53357,16 @@
           <t>阿玛尼 臻致丝绒哑光唇釉 #405 6.5ml（红管405）</t>
         </is>
       </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033887258.html</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -53094,6 +53374,16 @@
           <t>阿玛尼 臻致丝绒哑光唇釉 #415 6.5ml（红管415）</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10183990070830.html</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -53101,6 +53391,16 @@
           <t>兰蔻 菁纯丝绒雾面唇膏196 3.4g（哑光小蛮腰196）</t>
         </is>
       </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100012529857.html</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -53108,6 +53408,16 @@
           <t>兰蔻 菁纯丝绒雾面唇膏274 3.4g（哑光小蛮腰274）</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100192375838.html</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -53115,6 +53425,16 @@
           <t>兰蔻 菁纯丝绒雾面唇膏295 3.4g（哑光小蛮腰295）</t>
         </is>
       </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10118395377382.html</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -53122,6 +53442,16 @@
           <t>克丽丝汀迪奥 烈艳蓝金唇膏888哑光 3.5g</t>
         </is>
       </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100056057300.html</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -53129,6 +53459,16 @@
           <t>克丽丝汀迪奥 烈艳蓝金唇膏999缎光 3.5g</t>
         </is>
       </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100056057296.html</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -53136,6 +53476,16 @@
           <t>克丽丝汀迪奥 烈艳蓝金唇膏999丝绒 3.5g</t>
         </is>
       </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100077239849.html</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -53143,6 +53493,16 @@
           <t>克丽丝汀迪奥 烈艳蓝金唇膏999哑光 3.5g</t>
         </is>
       </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100056057296.html</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -53150,6 +53510,16 @@
           <t>克丽丝汀迪奥 烈艳蓝金唇膏720丝绒 3.5g</t>
         </is>
       </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100061748829.html</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -53157,6 +53527,16 @@
           <t>克丽丝汀迪奥 烈艳蓝金唇膏840丝绒 3.5g</t>
         </is>
       </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100077239849.html</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -53164,6 +53544,16 @@
           <t>克丽丝汀迪奥 烈艳蓝金唇膏772哑光 3.5g</t>
         </is>
       </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100077239849.html</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -53171,6 +53561,16 @@
           <t>克丽丝汀迪奥 魅惑润唇膏001号 3.2g</t>
         </is>
       </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100055466675.html</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -53178,6 +53578,16 @@
           <t>克丽丝汀迪奥 魅惑润唇膏004号 3.2g</t>
         </is>
       </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100055466687.html</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -53185,6 +53595,16 @@
           <t>纪梵希 高定香榭唇膏N306 3.4g</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100245236861.html</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -53192,6 +53612,16 @@
           <t>纪梵希 高定禁忌唇膏N333  3.4g</t>
         </is>
       </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10217756773159.html</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -53199,6 +53629,16 @@
           <t>纪梵希 高定香榭粉丝绒唇膏#N27 3.4g</t>
         </is>
       </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100012563721.html</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -53206,6 +53646,16 @@
           <t>圣罗兰 黑管唇釉416  5.5ml</t>
         </is>
       </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10214821580790.html</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -53213,6 +53663,16 @@
           <t>圣罗兰 细管纯口红#1988 2.2g（小金条1988）</t>
         </is>
       </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10215376166718.html</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -53220,6 +53680,16 @@
           <t>圣罗兰 细管纯口红#1936 2.2g（小金条1936）</t>
         </is>
       </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10214700640210.html</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -53227,6 +53697,16 @@
           <t>圣罗兰 细管纯口红#1966 2.2g（小金条1966）</t>
         </is>
       </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100029079354.html</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -53234,6 +53714,16 @@
           <t>圣罗兰 细管丝绒纯口红#302 2g（小黑条302）</t>
         </is>
       </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10214700742865.html</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -53241,6 +53731,16 @@
           <t>圣罗兰 细管丝绒纯口红#255 2g（小黑条255）</t>
         </is>
       </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100043000490.html</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -53248,6 +53748,16 @@
           <t>古驰 倾色华缎唇膏#25 3.5g（滋润）</t>
         </is>
       </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100095195980.html</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -53255,6 +53765,16 @@
           <t>古驰 倾色绒雾唇膏#25 3.5g（哑光）</t>
         </is>
       </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>160.55</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/1957773745.html</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -53262,6 +53782,16 @@
           <t>古驰 倾色丝润唇膏25 3.5g（碎花）</t>
         </is>
       </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10192018706251.html</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -53269,6 +53799,16 @@
           <t>古驰 倾色绒雾唇膏#208 3.5g（哑光）</t>
         </is>
       </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10113727019652.html</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -53276,6 +53816,16 @@
           <t>古驰 倾色绒雾唇膏#505 3.5g（哑光）</t>
         </is>
       </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10113727019650.html</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -53283,6 +53833,16 @@
           <t>古驰 倾色华缎唇膏#505 3.5g（缎光）</t>
         </is>
       </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100095195980.html</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -53290,6 +53850,16 @@
           <t>魅可 柔感哑光唇膏01 3g #602（CHILI小辣椒）</t>
         </is>
       </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10025624654583.html</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -53297,6 +53867,16 @@
           <t>魅可 丝绒哑光唇膏04 3g #707 (RubyWoo复古正红)</t>
         </is>
       </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10025624654585.html</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -53304,6 +53884,16 @@
           <t>魅可 经典柔感哑光唇膏05 3g #646 (MARRAKESH土橘色)</t>
         </is>
       </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100019145677.html</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -53311,6 +53901,16 @@
           <t>魅可 丝缎柔雾唇膏31 3g #916/316（DEVOTED TO CHLI柔雾小辣椒）</t>
         </is>
       </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033451064.html</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -53318,6 +53918,16 @@
           <t>魅可 丝缎柔雾唇膏41 3g #926 (DUBONNET BUZZ伯爵红茶)</t>
         </is>
       </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100018876057.html</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -53325,6 +53935,16 @@
           <t>兰蔻 奇迹香氛30ml</t>
         </is>
       </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10138101309693.html</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -53332,6 +53952,16 @@
           <t>兰蔻 是我香水50ml</t>
         </is>
       </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10118395239719.html</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -53374,6 +54004,16 @@
           <t>阿玛尼 自我无界香水 90ml</t>
         </is>
       </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033887468.html</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -53381,6 +54021,16 @@
           <t>阿玛尼 寄情男士香水（经典版） 50ml</t>
         </is>
       </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033887186.html</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -53388,6 +54038,16 @@
           <t>阿玛尼 寄情男士香水（经典版） 100ml</t>
         </is>
       </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033887222.html</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -53395,6 +54055,16 @@
           <t>克丽丝汀迪奥 迪奥小姐花漾淡香氛30ml</t>
         </is>
       </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100055252121.html</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -53402,6 +54072,16 @@
           <t>克丽丝汀迪奥 迪奥小姐花漾淡香氛50ml</t>
         </is>
       </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100047452792.html</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -53409,6 +54089,16 @@
           <t>克丽丝汀迪奥 迪奥小姐花漾淡香氛100ml</t>
         </is>
       </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100114122640.html</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -53416,6 +54106,16 @@
           <t>克丽丝汀迪奥 旷野男士淡香水60ml</t>
         </is>
       </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100061748791.html</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -53423,6 +54123,16 @@
           <t>克丽丝汀迪奥 旷野男士淡香水100ml</t>
         </is>
       </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100106933846.html</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -53430,6 +54140,16 @@
           <t>克丽丝汀迪奥 真我女士淡香水50ml</t>
         </is>
       </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100056935618.html</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -53437,6 +54157,16 @@
           <t>克丽丝汀迪奥 真我女士淡香水100ml</t>
         </is>
       </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100143734397.html</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -53444,6 +54174,16 @@
           <t>克丽丝汀迪奥 真我香氛30ml（浓香）</t>
         </is>
       </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100061748799.html</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -53451,6 +54191,16 @@
           <t>克丽丝汀迪奥 真我香氛50ml（浓香）</t>
         </is>
       </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100056935648.html</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -53458,6 +54208,16 @@
           <t>克丽丝汀迪奥 真我香氛100ml（浓香）</t>
         </is>
       </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100106933844.html</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -53465,6 +54225,16 @@
           <t>圣罗兰 自由之水经典版30ml</t>
         </is>
       </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100029082102.html</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -53472,6 +54242,16 @@
           <t>圣罗兰 自由之水经典版50ml</t>
         </is>
       </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100029081978.html</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -53479,6 +54259,16 @@
           <t>圣罗兰 自由之水经典版90ml</t>
         </is>
       </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>681.6</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10214673115261.html</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -53486,6 +54276,16 @@
           <t>圣罗兰 黑色奥飘茗女士香水30ml</t>
         </is>
       </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10215815501591.html</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -53493,6 +54293,16 @@
           <t>圣罗兰 黑色奥飘茗女士香水50ml</t>
         </is>
       </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10215815501592.html</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -53500,6 +54310,16 @@
           <t>圣罗兰 黑色奥飘茗女士香水90ml</t>
         </is>
       </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10215815501592.html</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -53507,6 +54327,16 @@
           <t>圣罗兰 反转巴黎光耀女士淡香水50ml</t>
         </is>
       </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100015958801.html</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -53514,6 +54344,16 @@
           <t>圣罗兰 新反转巴黎女士香水30ml</t>
         </is>
       </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100029082102.html</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -53521,6 +54361,16 @@
           <t>圣罗兰 新反转巴黎女士香水50ml</t>
         </is>
       </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100029081978.html</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -53528,6 +54378,16 @@
           <t>圣罗兰 新反转巴黎女士香水90ml</t>
         </is>
       </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10215815309734.html</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -53535,6 +54395,16 @@
           <t>祖玛珑 香水 30ml（蓝风铃香型）</t>
         </is>
       </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100022127217.html</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -53542,6 +54412,16 @@
           <t>祖玛珑 香水 30ml（鼠尾草与海盐香型）</t>
         </is>
       </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/10210339885479.html</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -53549,6 +54429,16 @@
           <t>祖玛珑 香水 30ml（英国梨与小苍兰香型）</t>
         </is>
       </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033356616.html</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -53556,11 +54446,31 @@
           <t>祖玛珑 香水 100ml（蓝风铃香型）</t>
         </is>
       </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033356620.html</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
           <t>祖玛珑 香水 100ml（鼠尾草与海盐香型）</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100033356614.html</t>
         </is>
       </c>
     </row>

--- a/spider_jd/标题.xlsx
+++ b/spider_jd/标题.xlsx
@@ -54480,6 +54480,16 @@
           <t>祖玛珑 香水 100ml（英国梨与小苍兰香型）</t>
         </is>
       </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100018812709.html</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -54487,6 +54497,16 @@
           <t>爱马仕 大地淡香水50ml</t>
         </is>
       </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100106283816.html</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -54494,6 +54514,16 @@
           <t>爱马仕 大地淡香水100ml</t>
         </is>
       </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100227921807.html</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -54501,6 +54531,16 @@
           <t>爱马仕 尼罗河香水30ml</t>
         </is>
       </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100329723188.html</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -54508,6 +54548,16 @@
           <t>爱马仕 尼罗河香水50ml</t>
         </is>
       </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100094711249.html</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -54515,6 +54565,16 @@
           <t>爱马仕 尼罗河花园香水100ml</t>
         </is>
       </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100213989949.html</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -54522,6 +54582,16 @@
           <t>爱马仕 李先生的花园系列淡香水 30ml</t>
         </is>
       </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100106716748.html</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -54529,6 +54599,16 @@
           <t>爱马仕 李先生的花园系列淡香水 50ml</t>
         </is>
       </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100106716788.html</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -54536,6 +54616,16 @@
           <t>爱马仕 李先生的花园系列淡香水 100ml</t>
         </is>
       </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100106716748.html</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -54543,6 +54633,16 @@
           <t>爱马仕 屋顶花园淡香水30ml</t>
         </is>
       </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100095061263.html</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -54550,11 +54650,31 @@
           <t>爱马仕 屋顶花园淡香水50ml</t>
         </is>
       </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100106410484.html</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
           <t>爱马仕 屋顶花园淡香水100ml</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/100094711253.html</t>
         </is>
       </c>
     </row>
